--- a/teacher_data.xlsx
+++ b/teacher_data.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="392">
   <si>
     <t>מספר זהות</t>
   </si>
@@ -75,9 +75,6 @@
     <t>דוד</t>
   </si>
   <si>
-    <t>1979-06-21</t>
-  </si>
-  <si>
     <t>שטרסר</t>
   </si>
   <si>
@@ -117,9 +114,6 @@
     <t>רויטל</t>
   </si>
   <si>
-    <t>1976-12-12</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
@@ -132,9 +126,6 @@
     <t>אברהם חיים</t>
   </si>
   <si>
-    <t>1991-03-16</t>
-  </si>
-  <si>
     <t>מיכה</t>
   </si>
   <si>
@@ -168,9 +159,6 @@
     <t>שרה</t>
   </si>
   <si>
-    <t>1992-11-09</t>
-  </si>
-  <si>
     <t>p0527113007@gmail.com</t>
   </si>
   <si>
@@ -186,9 +174,6 @@
     <t>אברהם</t>
   </si>
   <si>
-    <t>1978-05-18</t>
-  </si>
-  <si>
     <t>בעלי התוספות</t>
   </si>
   <si>
@@ -216,9 +201,6 @@
     <t>017854654</t>
   </si>
   <si>
-    <t>1980-07-12</t>
-  </si>
-  <si>
     <t>203210745</t>
   </si>
   <si>
@@ -228,9 +210,6 @@
     <t>אסתר</t>
   </si>
   <si>
-    <t>1991-06-18</t>
-  </si>
-  <si>
     <t>השלושה</t>
   </si>
   <si>
@@ -264,18 +243,12 @@
     <t>ישראל שמעון</t>
   </si>
   <si>
-    <t>1991-12-11</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
     <t>שרה רחל בריינא</t>
   </si>
   <si>
-    <t>1992-01-09</t>
-  </si>
-  <si>
     <t>0527113007</t>
   </si>
   <si>
@@ -291,9 +264,6 @@
     <t>אשר אנשל</t>
   </si>
   <si>
-    <t>1978-11-10</t>
-  </si>
-  <si>
     <t>בן עוזיאל</t>
   </si>
   <si>
@@ -315,9 +285,6 @@
     <t>יוכבד</t>
   </si>
   <si>
-    <t>1979-01-16</t>
-  </si>
-  <si>
     <t>14</t>
   </si>
   <si>
@@ -327,9 +294,6 @@
     <t>שפיצר</t>
   </si>
   <si>
-    <t>1972-11-07</t>
-  </si>
-  <si>
     <t>0548432666</t>
   </si>
   <si>
@@ -348,18 +312,12 @@
     <t>לאה</t>
   </si>
   <si>
-    <t>1976-04-20</t>
-  </si>
-  <si>
     <t>336070263</t>
   </si>
   <si>
     <t>מוזסון</t>
   </si>
   <si>
-    <t>1996-10-14</t>
-  </si>
-  <si>
     <t>אבן שפרוט</t>
   </si>
   <si>
@@ -375,9 +333,6 @@
     <t>316243146</t>
   </si>
   <si>
-    <t>1996-06-02</t>
-  </si>
-  <si>
     <t>21</t>
   </si>
   <si>
@@ -396,9 +351,6 @@
     <t>זיידל זלמן</t>
   </si>
   <si>
-    <t>1995-11-14</t>
-  </si>
-  <si>
     <t>רבינא</t>
   </si>
   <si>
@@ -417,18 +369,12 @@
     <t>דבורה</t>
   </si>
   <si>
-    <t>1998-01-20</t>
-  </si>
-  <si>
     <t>031168065</t>
   </si>
   <si>
     <t>גרבר</t>
   </si>
   <si>
-    <t>1979-12-31</t>
-  </si>
-  <si>
     <t>חידא</t>
   </si>
   <si>
@@ -447,9 +393,6 @@
     <t>035895861</t>
   </si>
   <si>
-    <t>1979-07-12</t>
-  </si>
-  <si>
     <t>059569764</t>
   </si>
   <si>
@@ -459,9 +402,6 @@
     <t>נפתלי</t>
   </si>
   <si>
-    <t>1965-04-24</t>
-  </si>
-  <si>
     <t>רוזנהיים</t>
   </si>
   <si>
@@ -480,9 +420,6 @@
     <t>אהובה</t>
   </si>
   <si>
-    <t>1966-04-26</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
@@ -498,9 +435,6 @@
     <t>משה צבי</t>
   </si>
   <si>
-    <t>1979-12-29</t>
-  </si>
-  <si>
     <t>חטיבת הנגב</t>
   </si>
   <si>
@@ -525,9 +459,6 @@
     <t>חנה</t>
   </si>
   <si>
-    <t>1978-05-01</t>
-  </si>
-  <si>
     <t>027384072</t>
   </si>
   <si>
@@ -537,9 +468,6 @@
     <t>יעקב ראובן</t>
   </si>
   <si>
-    <t>1974-11-28</t>
-  </si>
-  <si>
     <t>יונתן בן עוזיאל</t>
   </si>
   <si>
@@ -555,9 +483,6 @@
     <t>037145539</t>
   </si>
   <si>
-    <t>1979-10-02</t>
-  </si>
-  <si>
     <t>10</t>
   </si>
   <si>
@@ -567,9 +492,6 @@
     <t>וייס</t>
   </si>
   <si>
-    <t>1981-03-09</t>
-  </si>
-  <si>
     <t>רבי עקיבא</t>
   </si>
   <si>
@@ -588,18 +510,12 @@
     <t>039036413</t>
   </si>
   <si>
-    <t>1983-01-02</t>
-  </si>
-  <si>
     <t>11</t>
   </si>
   <si>
     <t>208924456</t>
   </si>
   <si>
-    <t>1997-02-28</t>
-  </si>
-  <si>
     <t>הרב שך</t>
   </si>
   <si>
@@ -615,18 +531,12 @@
     <t>315556613</t>
   </si>
   <si>
-    <t>1996-01-19</t>
-  </si>
-  <si>
     <t>035726652</t>
   </si>
   <si>
     <t>ווייס</t>
   </si>
   <si>
-    <t>1978-07-17</t>
-  </si>
-  <si>
     <t>89</t>
   </si>
   <si>
@@ -645,9 +555,6 @@
     <t>מרים</t>
   </si>
   <si>
-    <t>1980-07-07</t>
-  </si>
-  <si>
     <t>021767942</t>
   </si>
   <si>
@@ -657,9 +564,6 @@
     <t>יהודה אלעזר</t>
   </si>
   <si>
-    <t>1983-08-28</t>
-  </si>
-  <si>
     <t>18</t>
   </si>
   <si>
@@ -681,18 +585,12 @@
     <t>שרה רבקה</t>
   </si>
   <si>
-    <t>1984-07-07</t>
-  </si>
-  <si>
     <t>059178087</t>
   </si>
   <si>
     <t>ירוחם</t>
   </si>
   <si>
-    <t>1965-02-10</t>
-  </si>
-  <si>
     <t>רמבם</t>
   </si>
   <si>
@@ -711,9 +609,6 @@
     <t>יוסף יהודה</t>
   </si>
   <si>
-    <t>1979-03-19</t>
-  </si>
-  <si>
     <t>קדושת יום טוב</t>
   </si>
   <si>
@@ -726,9 +621,6 @@
     <t>יזשעף</t>
   </si>
   <si>
-    <t>1978-09-05</t>
-  </si>
-  <si>
     <t>058352352</t>
   </si>
   <si>
@@ -738,9 +630,6 @@
     <t>ברוך</t>
   </si>
   <si>
-    <t>1966-03-16</t>
-  </si>
-  <si>
     <t>אברהם בן דוד</t>
   </si>
   <si>
@@ -759,18 +648,12 @@
     <t>אסתר רחל</t>
   </si>
   <si>
-    <t>1969-03-29</t>
-  </si>
-  <si>
     <t>301760468</t>
   </si>
   <si>
     <t>אלטמן</t>
   </si>
   <si>
-    <t>1990-01-03</t>
-  </si>
-  <si>
     <t>חברון</t>
   </si>
   <si>
@@ -783,9 +666,6 @@
     <t>רננה</t>
   </si>
   <si>
-    <t>1992-08-13</t>
-  </si>
-  <si>
     <t>301115234</t>
   </si>
   <si>
@@ -795,9 +675,6 @@
     <t>חיים מאיר</t>
   </si>
   <si>
-    <t>1987-11-15</t>
-  </si>
-  <si>
     <t>גינות דוד</t>
   </si>
   <si>
@@ -813,18 +690,12 @@
     <t>רייזל שושנה</t>
   </si>
   <si>
-    <t>1987-09-06</t>
-  </si>
-  <si>
     <t>017879164</t>
   </si>
   <si>
     <t>פריד</t>
   </si>
   <si>
-    <t>1982-06-10</t>
-  </si>
-  <si>
     <t>נחמיה</t>
   </si>
   <si>
@@ -837,33 +708,21 @@
     <t>066758426</t>
   </si>
   <si>
-    <t>1984-04-19</t>
-  </si>
-  <si>
     <t>214382285</t>
   </si>
   <si>
-    <t>2003-08-28</t>
-  </si>
-  <si>
     <t>0556722191</t>
   </si>
   <si>
     <t>326590676</t>
   </si>
   <si>
-    <t>2004-05-28</t>
-  </si>
-  <si>
     <t>324953918</t>
   </si>
   <si>
     <t>זלצר</t>
   </si>
   <si>
-    <t>2002-06-30</t>
-  </si>
-  <si>
     <t>חבקוק</t>
   </si>
   <si>
@@ -879,18 +738,12 @@
     <t>בלומה</t>
   </si>
   <si>
-    <t>2003-04-27</t>
-  </si>
-  <si>
     <t>026579102</t>
   </si>
   <si>
     <t>פישמן</t>
   </si>
   <si>
-    <t>1986-09-04</t>
-  </si>
-  <si>
     <t>מינץ</t>
   </si>
   <si>
@@ -900,9 +753,6 @@
     <t>200400513</t>
   </si>
   <si>
-    <t>1988-03-31</t>
-  </si>
-  <si>
     <t>049820814</t>
   </si>
   <si>
@@ -912,9 +762,6 @@
     <t>מנחם יצחק</t>
   </si>
   <si>
-    <t>1982-03-19</t>
-  </si>
-  <si>
     <t>בעל שם טוב</t>
   </si>
   <si>
@@ -927,9 +774,6 @@
     <t>חיה מרים</t>
   </si>
   <si>
-    <t>1982-03-25</t>
-  </si>
-  <si>
     <t>41</t>
   </si>
   <si>
@@ -942,9 +786,6 @@
     <t>משה מרדכי</t>
   </si>
   <si>
-    <t>1994-11-24</t>
-  </si>
-  <si>
     <t>חתם סופר</t>
   </si>
   <si>
@@ -963,9 +804,6 @@
     <t>ברוך שלום</t>
   </si>
   <si>
-    <t>1996-08-17</t>
-  </si>
-  <si>
     <t>שבטי ישראל</t>
   </si>
   <si>
@@ -984,18 +822,12 @@
     <t>טויבא</t>
   </si>
   <si>
-    <t>2000-04-29</t>
-  </si>
-  <si>
     <t>021398938</t>
   </si>
   <si>
     <t>מיכאל</t>
   </si>
   <si>
-    <t>1980-06-02</t>
-  </si>
-  <si>
     <t>שמעיה</t>
   </si>
   <si>
@@ -1011,9 +843,6 @@
     <t>040866105</t>
   </si>
   <si>
-    <t>1981-02-20</t>
-  </si>
-  <si>
     <t>207986878</t>
   </si>
   <si>
@@ -1023,9 +852,6 @@
     <t>שלום</t>
   </si>
   <si>
-    <t>1999-04-03</t>
-  </si>
-  <si>
     <t>יצחק שדה</t>
   </si>
   <si>
@@ -1041,18 +867,12 @@
     <t>הינדא</t>
   </si>
   <si>
-    <t>1999-10-07</t>
-  </si>
-  <si>
     <t>014823454</t>
   </si>
   <si>
     <t>אולמן</t>
   </si>
   <si>
-    <t>1974-12-19</t>
-  </si>
-  <si>
     <t>רבי אבא</t>
   </si>
   <si>
@@ -1065,18 +885,12 @@
     <t>בלה</t>
   </si>
   <si>
-    <t>1975-02-23</t>
-  </si>
-  <si>
     <t>039693072</t>
   </si>
   <si>
     <t>רוט</t>
   </si>
   <si>
-    <t>1983-12-31</t>
-  </si>
-  <si>
     <t>0527683374</t>
   </si>
   <si>
@@ -1089,18 +903,12 @@
     <t>זיסי</t>
   </si>
   <si>
-    <t>1984-08-11</t>
-  </si>
-  <si>
     <t>211338223</t>
   </si>
   <si>
     <t>שפירא</t>
   </si>
   <si>
-    <t>2000-04-09</t>
-  </si>
-  <si>
     <t>גוטמכר</t>
   </si>
   <si>
@@ -1116,18 +924,12 @@
     <t>רבקי</t>
   </si>
   <si>
-    <t>2001-12-03</t>
-  </si>
-  <si>
     <t>208685636</t>
   </si>
   <si>
     <t>וסרבלט</t>
   </si>
   <si>
-    <t>1997-08-19</t>
-  </si>
-  <si>
     <t>הרב כהנמן</t>
   </si>
   <si>
@@ -1146,18 +948,12 @@
     <t>נחמה</t>
   </si>
   <si>
-    <t>1998-02-04</t>
-  </si>
-  <si>
     <t>301175691</t>
   </si>
   <si>
     <t>פרקש</t>
   </si>
   <si>
-    <t>1987-09-22</t>
-  </si>
-  <si>
     <t>נויפלד</t>
   </si>
   <si>
@@ -1170,9 +966,6 @@
     <t>303043319</t>
   </si>
   <si>
-    <t>1989-04-05</t>
-  </si>
-  <si>
     <t>214129264</t>
   </si>
   <si>
@@ -1182,9 +975,6 @@
     <t>שמעון דוב</t>
   </si>
   <si>
-    <t>2003-03-12</t>
-  </si>
-  <si>
     <t>הרב בלוי 10</t>
   </si>
   <si>
@@ -1200,18 +990,12 @@
     <t>רבקה מרים</t>
   </si>
   <si>
-    <t>2006-03-21</t>
-  </si>
-  <si>
     <t>028462091</t>
   </si>
   <si>
     <t>יהושע</t>
   </si>
   <si>
-    <t>1971-02-16</t>
-  </si>
-  <si>
     <t>דרך מנחם בגין</t>
   </si>
   <si>
@@ -1230,18 +1014,12 @@
     <t>חוה</t>
   </si>
   <si>
-    <t>1969-09-09</t>
-  </si>
-  <si>
     <t>315448829</t>
   </si>
   <si>
     <t>רובין</t>
   </si>
   <si>
-    <t>1996-12-29</t>
-  </si>
-  <si>
     <t>72</t>
   </si>
   <si>
@@ -1254,18 +1032,12 @@
     <t>208934661</t>
   </si>
   <si>
-    <t>1996-11-19</t>
-  </si>
-  <si>
     <t>207647868</t>
   </si>
   <si>
     <t>דב</t>
   </si>
   <si>
-    <t>2000-08-10</t>
-  </si>
-  <si>
     <t>עזרא</t>
   </si>
   <si>
@@ -1281,18 +1053,12 @@
     <t>אלטע פעסיל</t>
   </si>
   <si>
-    <t>1997-02-07</t>
-  </si>
-  <si>
     <t>037202561</t>
   </si>
   <si>
     <t>קליינר</t>
   </si>
   <si>
-    <t>1981-05-24</t>
-  </si>
-  <si>
     <t>ברטנורה</t>
   </si>
   <si>
@@ -1311,9 +1077,6 @@
     <t>אליאור</t>
   </si>
   <si>
-    <t>1983-03-24</t>
-  </si>
-  <si>
     <t>צבי אלימלך</t>
   </si>
   <si>
@@ -1323,9 +1086,6 @@
     <t>זילברברג</t>
   </si>
   <si>
-    <t>1985-06-07</t>
-  </si>
-  <si>
     <t>0504105206</t>
   </si>
   <si>
@@ -1338,9 +1098,6 @@
     <t>ברינה</t>
   </si>
   <si>
-    <t>1985-08-31</t>
-  </si>
-  <si>
     <t>022973531</t>
   </si>
   <si>
@@ -1350,27 +1107,18 @@
     <t>יוסף נפתלי</t>
   </si>
   <si>
-    <t>1967-03-19</t>
-  </si>
-  <si>
     <t>0556757390</t>
   </si>
   <si>
     <t>טובי</t>
   </si>
   <si>
-    <t>1972-12-08</t>
-  </si>
-  <si>
     <t>216015966</t>
   </si>
   <si>
     <t>דנדרוביץ</t>
   </si>
   <si>
-    <t>2006-01-16</t>
-  </si>
-  <si>
     <t>ר עקיבא</t>
   </si>
   <si>
@@ -1386,18 +1134,12 @@
     <t>215556325</t>
   </si>
   <si>
-    <t>2005-10-09</t>
-  </si>
-  <si>
     <t>323050765</t>
   </si>
   <si>
     <t>לידר</t>
   </si>
   <si>
-    <t>2001-06-30</t>
-  </si>
-  <si>
     <t>0534147056</t>
   </si>
   <si>
@@ -1407,18 +1149,12 @@
     <t>214279671</t>
   </si>
   <si>
-    <t>2000-01-01</t>
-  </si>
-  <si>
     <t>325088847</t>
   </si>
   <si>
     <t>זילברשלג</t>
   </si>
   <si>
-    <t>2002-09-09</t>
-  </si>
-  <si>
     <t>דמשק אליעזר</t>
   </si>
   <si>
@@ -1435,9 +1171,6 @@
   </si>
   <si>
     <t>גולדה הענא</t>
-  </si>
-  <si>
-    <t>2004-04-15</t>
   </si>
   <si>
     <t>סניף</t>
@@ -1512,9 +1245,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1826,7 +1561,7 @@
     <col min="2" max="2" width="14.8984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.8984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.296875" style="3" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.69921875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.796875" bestFit="1" customWidth="1"/>
@@ -1837,13 +1572,13 @@
     <col min="14" max="14" width="8.3984375" customWidth="1"/>
     <col min="15" max="16" width="15.796875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="16.3984375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.19921875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.796875" style="3" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>473</v>
+        <v>384</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1854,11 +1589,11 @@
       <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>479</v>
+        <v>390</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -1882,7 +1617,7 @@
         <v>10</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>478</v>
+        <v>389</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>11</v>
@@ -1893,7 +1628,7 @@
       <c r="Q1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1908,2460 +1643,2460 @@
       <c r="D2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="2">
+        <v>29027</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>23</v>
-      </c>
       <c r="K2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="M2" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="N2" s="1">
         <v>8</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
+      </c>
+      <c r="R2" s="2">
+        <v>28106</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="E3" s="2">
+        <v>33313</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="J3" s="1"/>
       <c r="K3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N3" s="1">
         <v>7</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="R3" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
+      </c>
+      <c r="R3" s="2">
+        <v>33917</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="2">
+        <v>28628</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="J4" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="M4" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="M4" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="N4" s="1">
         <v>9</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>65</v>
+        <v>40</v>
+      </c>
+      <c r="R4" s="2">
+        <v>29414</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>69</v>
+        <v>62</v>
+      </c>
+      <c r="E5" s="2">
+        <v>33407</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="J5" s="1"/>
       <c r="K5" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="N5" s="1">
         <v>6</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>81</v>
+        <v>73</v>
+      </c>
+      <c r="R5" s="2">
+        <v>33583</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="2">
+        <v>33612</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="N6" s="1">
         <v>7</v>
       </c>
       <c r="O6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="P6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>37</v>
+      <c r="R6" s="2">
+        <v>33313</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>90</v>
+        <v>80</v>
+      </c>
+      <c r="E7" s="2">
+        <v>28804</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="J7" s="1"/>
       <c r="K7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="N7" s="1">
         <v>7</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>98</v>
+        <v>87</v>
+      </c>
+      <c r="R7" s="2">
+        <v>28871</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>102</v>
+        <v>58</v>
+      </c>
+      <c r="E8" s="2">
+        <v>26610</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="N8" s="1">
         <v>3</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>109</v>
+        <v>96</v>
+      </c>
+      <c r="R8" s="2">
+        <v>27870</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>112</v>
+        <v>69</v>
+      </c>
+      <c r="E9" s="2">
+        <v>35352</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="N9" s="1">
         <v>2</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>118</v>
+        <v>45</v>
+      </c>
+      <c r="R9" s="2">
+        <v>35218</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>125</v>
+        <v>109</v>
+      </c>
+      <c r="E10" s="2">
+        <v>35017</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="N10" s="1">
         <v>4</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>123</v>
+        <v>108</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>132</v>
+        <v>115</v>
+      </c>
+      <c r="R10" s="2">
+        <v>35815</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>133</v>
+        <v>116</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>135</v>
+        <v>26</v>
+      </c>
+      <c r="E11" s="2">
+        <v>29220</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="N11" s="1">
         <v>2</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>142</v>
+        <v>40</v>
+      </c>
+      <c r="R11" s="2">
+        <v>29048</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>146</v>
+        <v>126</v>
+      </c>
+      <c r="E12" s="2">
+        <v>23856</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>153</v>
+        <v>132</v>
+      </c>
+      <c r="R12" s="2">
+        <v>24223</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>159</v>
+        <v>137</v>
+      </c>
+      <c r="E13" s="2">
+        <v>29218</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>164</v>
+        <v>142</v>
       </c>
       <c r="K13" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="M13" s="1"/>
       <c r="N13" s="1">
         <v>9</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>168</v>
+        <v>145</v>
+      </c>
+      <c r="R13" s="2">
+        <v>28611</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>169</v>
+        <v>146</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>172</v>
+        <v>148</v>
+      </c>
+      <c r="E14" s="2">
+        <v>27361</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>175</v>
+        <v>151</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="N14" s="1">
         <v>5</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>178</v>
+        <v>70</v>
+      </c>
+      <c r="R14" s="2">
+        <v>29130</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>182</v>
+        <v>122</v>
+      </c>
+      <c r="E15" s="2">
+        <v>29654</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>185</v>
+        <v>159</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="N15" s="1">
         <v>7</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>189</v>
+        <v>94</v>
+      </c>
+      <c r="R15" s="2">
+        <v>30318</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>191</v>
+        <v>164</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>192</v>
+        <v>41</v>
+      </c>
+      <c r="E16" s="2">
+        <v>35489</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>193</v>
+        <v>165</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>194</v>
+        <v>166</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="J16" s="1"/>
       <c r="K16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>196</v>
+        <v>168</v>
       </c>
       <c r="N16" s="1">
         <v>3</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>198</v>
+        <v>96</v>
+      </c>
+      <c r="R16" s="2">
+        <v>35083</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>201</v>
+        <v>27</v>
+      </c>
+      <c r="E17" s="2">
+        <v>28688</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>480</v>
+        <v>391</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>202</v>
+        <v>172</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>203</v>
+        <v>173</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>204</v>
+        <v>174</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>205</v>
+        <v>175</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M17" s="1"/>
       <c r="N17" s="1">
         <v>12</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>206</v>
+        <v>176</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>208</v>
+        <v>177</v>
+      </c>
+      <c r="R17" s="2">
+        <v>29409</v>
       </c>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>212</v>
+        <v>180</v>
+      </c>
+      <c r="E18" s="2">
+        <v>30556</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="N18" s="1">
         <v>7</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>218</v>
+        <v>186</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>220</v>
+        <v>187</v>
+      </c>
+      <c r="R18" s="2">
+        <v>30870</v>
       </c>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>221</v>
+        <v>188</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>475</v>
+        <v>386</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>223</v>
+        <v>189</v>
+      </c>
+      <c r="E19" s="2">
+        <v>23783</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>224</v>
+        <v>190</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>225</v>
+        <v>191</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>226</v>
+        <v>192</v>
       </c>
       <c r="J19" s="1"/>
       <c r="K19" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M19" s="1"/>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
+      <c r="R19" s="2"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>228</v>
+        <v>194</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>230</v>
+        <v>195</v>
+      </c>
+      <c r="E20" s="2">
+        <v>28933</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>231</v>
+        <v>196</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M20" s="1"/>
       <c r="N20" s="1">
         <v>4</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>233</v>
+        <v>198</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>234</v>
+        <v>199</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>235</v>
+        <v>62</v>
+      </c>
+      <c r="R20" s="2">
+        <v>28738</v>
       </c>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>239</v>
+        <v>202</v>
+      </c>
+      <c r="E21" s="2">
+        <v>24182</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>241</v>
+        <v>204</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>242</v>
+        <v>205</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L21" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="M21" s="1" t="s">
-        <v>243</v>
+        <v>206</v>
       </c>
       <c r="N21" s="1"/>
       <c r="O21" s="1" t="s">
-        <v>244</v>
+        <v>207</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>246</v>
+        <v>208</v>
+      </c>
+      <c r="R21" s="2">
+        <v>25291</v>
       </c>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>247</v>
+        <v>209</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>248</v>
+        <v>210</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>249</v>
+        <v>71</v>
+      </c>
+      <c r="E22" s="2">
+        <v>32876</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>250</v>
+        <v>211</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>119</v>
+        <v>104</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>251</v>
+        <v>212</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="M22" s="1"/>
       <c r="N22" s="1">
         <v>5</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>252</v>
+        <v>213</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>248</v>
+        <v>210</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>254</v>
+        <v>214</v>
+      </c>
+      <c r="R22" s="2">
+        <v>33829</v>
       </c>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>258</v>
+        <v>217</v>
+      </c>
+      <c r="E23" s="2">
+        <v>32096</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>259</v>
+        <v>218</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>260</v>
+        <v>219</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>261</v>
+        <v>220</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="M23" s="1"/>
       <c r="N23" s="1">
         <v>7</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>262</v>
+        <v>221</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>264</v>
+        <v>222</v>
+      </c>
+      <c r="R23" s="2">
+        <v>32026</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>265</v>
+        <v>223</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>266</v>
+        <v>224</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>267</v>
+        <v>185</v>
+      </c>
+      <c r="E24" s="2">
+        <v>30112</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>268</v>
+        <v>225</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>269</v>
+        <v>226</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M24" s="1"/>
       <c r="N24" s="1">
         <v>7</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>271</v>
+        <v>228</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>266</v>
+        <v>224</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>272</v>
+        <v>145</v>
+      </c>
+      <c r="R24" s="2">
+        <v>30791</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>273</v>
+        <v>229</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>274</v>
+        <v>68</v>
+      </c>
+      <c r="E25" s="2">
+        <v>37861</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>190</v>
+        <v>163</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>275</v>
+        <v>230</v>
       </c>
       <c r="J25" s="1"/>
       <c r="K25" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M25" s="1"/>
       <c r="N25" s="1">
         <v>1</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>276</v>
+        <v>231</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="Q25" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R25" s="1" t="s">
-        <v>277</v>
+      <c r="R25" s="2">
+        <v>38135</v>
       </c>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>278</v>
+        <v>232</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>279</v>
+        <v>233</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>280</v>
+        <v>26</v>
+      </c>
+      <c r="E26" s="2">
+        <v>37437</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>281</v>
+        <v>234</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>282</v>
+        <v>235</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>283</v>
+        <v>236</v>
       </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1" t="s">
-        <v>284</v>
+        <v>237</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>279</v>
+        <v>233</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>286</v>
+        <v>238</v>
+      </c>
+      <c r="R26" s="2">
+        <v>37738</v>
       </c>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>287</v>
+        <v>239</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>289</v>
+        <v>50</v>
+      </c>
+      <c r="E27" s="2">
+        <v>31659</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>290</v>
+        <v>241</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>291</v>
+        <v>242</v>
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M27" s="1"/>
       <c r="N27" s="1">
         <v>7</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>292</v>
+        <v>243</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>288</v>
+        <v>240</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>293</v>
+        <v>57</v>
+      </c>
+      <c r="R27" s="2">
+        <v>32233</v>
       </c>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>294</v>
+        <v>244</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>295</v>
+        <v>245</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>297</v>
+        <v>246</v>
+      </c>
+      <c r="E28" s="2">
+        <v>30029</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>298</v>
+        <v>247</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>299</v>
+        <v>248</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M28" s="1"/>
       <c r="N28" s="1">
         <v>1</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>300</v>
+        <v>249</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>295</v>
+        <v>245</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="R28" s="1" t="s">
-        <v>302</v>
+        <v>250</v>
+      </c>
+      <c r="R28" s="2">
+        <v>30035</v>
       </c>
     </row>
     <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>304</v>
+        <v>252</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>305</v>
+        <v>253</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>307</v>
+        <v>254</v>
+      </c>
+      <c r="E29" s="2">
+        <v>34662</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>308</v>
+        <v>255</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>309</v>
+        <v>256</v>
       </c>
       <c r="J29" s="1"/>
       <c r="K29" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>310</v>
+        <v>257</v>
       </c>
       <c r="N29" s="1"/>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
+      <c r="R29" s="2"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>311</v>
+        <v>258</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>312</v>
+        <v>259</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>314</v>
+        <v>260</v>
+      </c>
+      <c r="E30" s="2">
+        <v>35294</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>315</v>
+        <v>261</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>316</v>
+        <v>262</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>317</v>
+        <v>263</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="N30" s="1">
         <v>3</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>319</v>
+        <v>265</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>312</v>
+        <v>259</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>321</v>
+        <v>266</v>
+      </c>
+      <c r="R30" s="2">
+        <v>36645</v>
       </c>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>322</v>
+        <v>267</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>324</v>
+        <v>268</v>
+      </c>
+      <c r="E31" s="2">
+        <v>29374</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>325</v>
+        <v>269</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>174</v>
+        <v>150</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>326</v>
+        <v>270</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>327</v>
+        <v>271</v>
       </c>
       <c r="K31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="M31" s="1" t="s">
-        <v>328</v>
+        <v>272</v>
       </c>
       <c r="N31" s="1">
         <v>7</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>329</v>
+        <v>273</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>330</v>
+        <v>177</v>
+      </c>
+      <c r="R31" s="2">
+        <v>29637</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>331</v>
+        <v>274</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>476</v>
+        <v>387</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>334</v>
+        <v>276</v>
+      </c>
+      <c r="E32" s="2">
+        <v>36253</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>335</v>
+        <v>277</v>
       </c>
       <c r="G32" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="I32" s="1" t="s">
-        <v>336</v>
+        <v>278</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>337</v>
+        <v>279</v>
       </c>
       <c r="N32" s="1">
         <v>3</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>338</v>
+        <v>280</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>332</v>
+        <v>275</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="R32" s="1" t="s">
-        <v>340</v>
+        <v>281</v>
+      </c>
+      <c r="R32" s="2">
+        <v>36440</v>
       </c>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>341</v>
+        <v>282</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>342</v>
+        <v>283</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>343</v>
+        <v>352</v>
+      </c>
+      <c r="E33" s="2">
+        <v>27382</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>344</v>
+        <v>284</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>345</v>
+        <v>285</v>
       </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M33" s="1"/>
       <c r="N33" s="1">
         <v>4</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>346</v>
+        <v>286</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>342</v>
+        <v>283</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="R33" s="1" t="s">
-        <v>348</v>
+        <v>287</v>
+      </c>
+      <c r="R33" s="2">
+        <v>27448</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>349</v>
+        <v>288</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>350</v>
+        <v>289</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>351</v>
+        <v>113</v>
+      </c>
+      <c r="E34" s="2">
+        <v>30681</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>231</v>
+        <v>196</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>352</v>
+        <v>290</v>
       </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M34" s="1"/>
       <c r="N34" s="1">
         <v>5</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>354</v>
+        <v>292</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>350</v>
+        <v>289</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>355</v>
-      </c>
-      <c r="R34" s="1" t="s">
-        <v>356</v>
+        <v>293</v>
+      </c>
+      <c r="R34" s="2">
+        <v>30905</v>
       </c>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>357</v>
+        <v>294</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>358</v>
+        <v>295</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>359</v>
+        <v>122</v>
+      </c>
+      <c r="E35" s="2">
+        <v>36625</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>360</v>
+        <v>296</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>361</v>
+        <v>297</v>
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>362</v>
+        <v>298</v>
       </c>
       <c r="N35" s="1">
         <v>2</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>363</v>
+        <v>299</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>358</v>
+        <v>295</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="R35" s="1" t="s">
-        <v>365</v>
+        <v>300</v>
+      </c>
+      <c r="R35" s="2">
+        <v>37228</v>
       </c>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>366</v>
+        <v>301</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>367</v>
+        <v>302</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>368</v>
+        <v>143</v>
+      </c>
+      <c r="E36" s="2">
+        <v>35661</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>369</v>
+        <v>303</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>370</v>
+        <v>304</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>371</v>
+        <v>305</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>372</v>
+        <v>306</v>
       </c>
       <c r="N36" s="1">
         <v>2</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>373</v>
+        <v>307</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>367</v>
+        <v>302</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="R36" s="1" t="s">
-        <v>375</v>
+        <v>308</v>
+      </c>
+      <c r="R36" s="2">
+        <v>35830</v>
       </c>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>376</v>
+        <v>309</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>377</v>
+        <v>310</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>378</v>
+        <v>69</v>
+      </c>
+      <c r="E37" s="2">
+        <v>32042</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>379</v>
+        <v>311</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>380</v>
+        <v>312</v>
       </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="M37" s="1" t="s">
-        <v>381</v>
+        <v>313</v>
       </c>
       <c r="N37" s="1">
         <v>7</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>382</v>
+        <v>314</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>377</v>
+        <v>310</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="R37" s="1" t="s">
-        <v>383</v>
+        <v>40</v>
+      </c>
+      <c r="R37" s="2">
+        <v>32603</v>
       </c>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>384</v>
+        <v>315</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>385</v>
+        <v>316</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>387</v>
+        <v>317</v>
+      </c>
+      <c r="E38" s="2">
+        <v>37692</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>388</v>
+        <v>318</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>389</v>
+        <v>319</v>
       </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="N38" s="1"/>
       <c r="O38" s="1" t="s">
-        <v>391</v>
+        <v>321</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>385</v>
+        <v>316</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="R38" s="1" t="s">
-        <v>393</v>
+        <v>322</v>
+      </c>
+      <c r="R38" s="2">
+        <v>38797</v>
       </c>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>394</v>
+        <v>323</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>477</v>
+        <v>388</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>395</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>396</v>
+        <v>324</v>
+      </c>
+      <c r="E39" s="2">
+        <v>25980</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>397</v>
+        <v>325</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>398</v>
+        <v>326</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>399</v>
+        <v>327</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>400</v>
+        <v>328</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1" t="s">
-        <v>401</v>
+        <v>329</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>358</v>
+        <v>295</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="R39" s="1" t="s">
-        <v>403</v>
+        <v>330</v>
+      </c>
+      <c r="R39" s="2">
+        <v>25455</v>
       </c>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>404</v>
+        <v>331</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>406</v>
+        <v>42</v>
+      </c>
+      <c r="E40" s="2">
+        <v>35428</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>183</v>
+        <v>157</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>407</v>
+        <v>333</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>408</v>
+        <v>334</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>409</v>
+        <v>335</v>
       </c>
       <c r="N40" s="1">
         <v>3</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>410</v>
+        <v>336</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>405</v>
+        <v>332</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="R40" s="1" t="s">
-        <v>411</v>
+        <v>330</v>
+      </c>
+      <c r="R40" s="2">
+        <v>35388</v>
       </c>
     </row>
     <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>412</v>
+        <v>337</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>413</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>414</v>
+        <v>338</v>
+      </c>
+      <c r="E41" s="2">
+        <v>36748</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>415</v>
+        <v>339</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>416</v>
+        <v>340</v>
       </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L41" s="1" t="s">
-        <v>25</v>
-      </c>
       <c r="M41" s="1" t="s">
-        <v>417</v>
+        <v>341</v>
       </c>
       <c r="N41" s="1">
         <v>1</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>418</v>
+        <v>342</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>170</v>
+        <v>147</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="R41" s="1" t="s">
-        <v>420</v>
+        <v>343</v>
+      </c>
+      <c r="R41" s="2">
+        <v>35468</v>
       </c>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>421</v>
+        <v>344</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>422</v>
+        <v>345</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>423</v>
+        <v>28</v>
+      </c>
+      <c r="E42" s="2">
+        <v>29730</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>424</v>
+        <v>346</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>425</v>
+        <v>347</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>426</v>
+        <v>348</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>427</v>
+        <v>349</v>
       </c>
       <c r="N42" s="1">
         <v>7</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>428</v>
+        <v>350</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>422</v>
+        <v>345</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="R42" s="1" t="s">
-        <v>430</v>
+        <v>351</v>
+      </c>
+      <c r="R42" s="2">
+        <v>30399</v>
       </c>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>432</v>
+        <v>353</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>433</v>
+        <v>354</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>434</v>
+        <v>50</v>
+      </c>
+      <c r="E43" s="2">
+        <v>31205</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>435</v>
+        <v>355</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>435</v>
+        <v>355</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>436</v>
+        <v>356</v>
       </c>
       <c r="N43" s="1">
         <v>6</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>437</v>
+        <v>357</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>433</v>
+        <v>354</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>439</v>
+        <v>358</v>
+      </c>
+      <c r="R43" s="2">
+        <v>31290</v>
       </c>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>440</v>
+        <v>359</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>441</v>
+        <v>360</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>443</v>
+        <v>361</v>
+      </c>
+      <c r="E44" s="2">
+        <v>24550</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>224</v>
+        <v>190</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>444</v>
+        <v>362</v>
       </c>
       <c r="J44" s="1"/>
       <c r="K44" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1" t="s">
-        <v>441</v>
+        <v>360</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="R44" s="1" t="s">
-        <v>446</v>
+        <v>363</v>
+      </c>
+      <c r="R44" s="2">
+        <v>26641</v>
       </c>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>447</v>
+        <v>364</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>448</v>
+        <v>365</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>449</v>
+        <v>62</v>
+      </c>
+      <c r="E45" s="2">
+        <v>38733</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>450</v>
+        <v>366</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>451</v>
+        <v>367</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>452</v>
+        <v>368</v>
       </c>
       <c r="J45" s="1"/>
       <c r="K45" s="1" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>453</v>
+        <v>369</v>
       </c>
       <c r="N45" s="1"/>
       <c r="O45" s="1" t="s">
-        <v>454</v>
+        <v>370</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>448</v>
+        <v>365</v>
       </c>
       <c r="Q45" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R45" s="1" t="s">
-        <v>455</v>
+      <c r="R45" s="2">
+        <v>38634</v>
       </c>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>456</v>
+        <v>371</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>457</v>
+        <v>372</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>458</v>
+        <v>122</v>
+      </c>
+      <c r="E46" s="2">
+        <v>37072</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>224</v>
+        <v>190</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>459</v>
+        <v>373</v>
       </c>
       <c r="J46" s="1"/>
       <c r="K46" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>460</v>
+        <v>374</v>
       </c>
       <c r="N46" s="1"/>
       <c r="O46" s="1" t="s">
-        <v>461</v>
+        <v>375</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>457</v>
+        <v>372</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="R46" s="1" t="s">
-        <v>462</v>
+        <v>291</v>
+      </c>
+      <c r="R46" s="2">
+        <v>36526</v>
       </c>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>463</v>
+        <v>376</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>464</v>
+        <v>377</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>465</v>
+        <v>122</v>
+      </c>
+      <c r="E47" s="2">
+        <v>37508</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>466</v>
+        <v>378</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>303</v>
+        <v>251</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>467</v>
+        <v>379</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>468</v>
+        <v>380</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>469</v>
+        <v>381</v>
       </c>
       <c r="N47" s="1">
         <v>2</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>470</v>
+        <v>382</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>464</v>
+        <v>377</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="R47" s="1" t="s">
-        <v>472</v>
+        <v>383</v>
+      </c>
+      <c r="R47" s="2">
+        <v>38092</v>
       </c>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="1" t="s">
-        <v>474</v>
+        <v>385</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="E48" s="1"/>
+        <v>227</v>
+      </c>
+      <c r="E48" s="2"/>
       <c r="F48" s="1" t="s">
-        <v>231</v>
+        <v>196</v>
       </c>
       <c r="G48" s="1"/>
       <c r="H48" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I48" s="1">
         <v>504130077</v>
       </c>
       <c r="J48" s="1"/>
       <c r="K48" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
@@ -4369,7 +4104,7 @@
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
-      <c r="R48" s="1"/>
+      <c r="R48" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
